--- a/outputs/problem4/result_problem4.xlsx
+++ b/outputs/problem4/result_problem4.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.800000000000001</v>
+        <v>25.8</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3</v>
+        <v>26.2</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.4</v>
+        <v>26.3</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>26.7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>38.3</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5</v>
+        <v>38.7</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -590,7 +590,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.6</v>
+        <v>41.5</v>
       </c>
       <c r="E5" t="n">
-        <v>12.1</v>
+        <v>41.9</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -616,19 +616,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>46.9</v>
       </c>
       <c r="E6" t="n">
-        <v>12.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="7">
@@ -637,19 +637,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>49.3</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="8">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.4</v>
+        <v>279.2</v>
       </c>
       <c r="E8" t="n">
-        <v>26.9</v>
+        <v>279.6</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -688,199 +688,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>282.5</v>
       </c>
       <c r="E9" t="n">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>S11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>57.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>183.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>281.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>282</v>
-      </c>
-      <c r="E17" t="n">
-        <v>282.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>283.4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>284.9</v>
+        <v>282.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/problem4/result_problem4.xlsx
+++ b/outputs/problem4/result_problem4.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="E2" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="E5" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
